--- a/data/trans_orig/P13_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71744</t>
+          <t>72374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78234</t>
+          <t>77802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113748</t>
+          <t>115345</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126000</t>
+          <t>126337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174522</t>
+          <t>174716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>959979</t>
+          <t>959349</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>989681</t>
+          <t>988862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1201365</t>
+          <t>1199768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1236879</t>
+          <t>1237311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2172313</t>
+          <t>2172119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2220835</t>
+          <t>2220498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51595</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37244</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65579</t>
+          <t>67648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73155</t>
+          <t>72995</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111134</t>
+          <t>110867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1641818</t>
+          <t>1639459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1666249</t>
+          <t>1665784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1522094</t>
+          <t>1520025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1550429</t>
+          <t>1549021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3169952</t>
+          <t>3170219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3207931</t>
+          <t>3208091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28654</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532386</t>
+          <t>532113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546731</t>
+          <t>546558</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447758</t>
+          <t>448091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>465323</t>
+          <t>465220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>986982</t>
+          <t>986523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1007875</t>
+          <t>1007718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85961</t>
+          <t>86111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125506</t>
+          <t>127563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>140887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189635</t>
+          <t>192328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>238296</t>
+          <t>237495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303755</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3151037</t>
+          <t>3148980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3190582</t>
+          <t>3190432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3189562</t>
+          <t>3186869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3242186</t>
+          <t>3238310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6351986</t>
+          <t>6354738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6417445</t>
+          <t>6418246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53853</t>
+          <t>55751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89993</t>
+          <t>90527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173958</t>
+          <t>176058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226968</t>
+          <t>228953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239379</t>
+          <t>241447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303052</t>
+          <t>304594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>883685</t>
+          <t>883151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>919825</t>
+          <t>917927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1109731</t>
+          <t>1107746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1162741</t>
+          <t>1160641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2007324</t>
+          <t>2005782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2070997</t>
+          <t>2068929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59073</t>
+          <t>59194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96434</t>
+          <t>94701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91609</t>
+          <t>90226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135090</t>
+          <t>132975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159747</t>
+          <t>161703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>217204</t>
+          <t>217308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1865546</t>
+          <t>1867279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1902907</t>
+          <t>1902786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1620758</t>
+          <t>1622873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1664239</t>
+          <t>1665622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3500624</t>
+          <t>3500520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3558081</t>
+          <t>3556125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26120</t>
+          <t>26376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43214</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>458457</t>
+          <t>457617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473590</t>
+          <t>474113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>432511</t>
+          <t>432255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449516</t>
+          <t>450008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>896599</t>
+          <t>896656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>920180</t>
+          <t>920401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134151</t>
+          <t>134848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185426</t>
+          <t>187010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>294577</t>
+          <t>292961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361267</t>
+          <t>363203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443556</t>
+          <t>446865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>533177</t>
+          <t>534063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3231413</t>
+          <t>3229829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3282688</t>
+          <t>3281991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3189911</t>
+          <t>3187975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3256601</t>
+          <t>3258217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6434840</t>
+          <t>6433954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6524461</t>
+          <t>6521152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>33496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>59597</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86697</t>
+          <t>86696</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126627</t>
+          <t>127271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127762</t>
+          <t>127173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174872</t>
+          <t>175286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695402</t>
+          <t>694750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>720111</t>
+          <t>720851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>865917</t>
+          <t>865273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>905847</t>
+          <t>905848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1572019</t>
+          <t>1571605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1619129</t>
+          <t>1619718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44595</t>
+          <t>42971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77110</t>
+          <t>76213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55494</t>
+          <t>54041</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90434</t>
+          <t>88501</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107980</t>
+          <t>107506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153848</t>
+          <t>153648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1998302</t>
+          <t>1999199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2030817</t>
+          <t>2032441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1896811</t>
+          <t>1898744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1931751</t>
+          <t>1933204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3908810</t>
+          <t>3909010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3954678</t>
+          <t>3955152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>22832</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>48097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524582</t>
+          <t>524054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540357</t>
+          <t>540049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>518149</t>
+          <t>517038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536914</t>
+          <t>536395</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1047970</t>
+          <t>1046062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073047</t>
+          <t>1071692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95224</t>
+          <t>98048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141781</t>
+          <t>140993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168395</t>
+          <t>169542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227271</t>
+          <t>223629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276423</t>
+          <t>280127</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348098</t>
+          <t>349906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3234864</t>
+          <t>3235652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3281421</t>
+          <t>3278597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3299791</t>
+          <t>3303433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3358667</t>
+          <t>3357520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6555609</t>
+          <t>6553801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6627284</t>
+          <t>6623580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50148</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78729</t>
+          <t>76725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120470</t>
+          <t>119161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>151546</t>
+          <t>149221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177115</t>
+          <t>176126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217480</t>
+          <t>217076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435338</t>
+          <t>437342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>463919</t>
+          <t>462809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600873</t>
+          <t>603198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631949</t>
+          <t>633258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1049006</t>
+          <t>1049410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1089371</t>
+          <t>1090360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54291</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99761</t>
+          <t>98649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69505</t>
+          <t>71751</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116605</t>
+          <t>119766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139443</t>
+          <t>141726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208767</t>
+          <t>207755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2188532</t>
+          <t>2189644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2234002</t>
+          <t>2234432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2119737</t>
+          <t>2116576</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2166837</t>
+          <t>2164591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4315868</t>
+          <t>4316880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4385192</t>
+          <t>4382909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37757</t>
+          <t>36649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>33822</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57178</t>
+          <t>58296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608866</t>
+          <t>609974</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630024</t>
+          <t>630019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633563</t>
+          <t>633279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>646522</t>
+          <t>647421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249908</t>
+          <t>1248790</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1273349</t>
+          <t>1273264</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>127411</t>
+          <t>129970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197834</t>
+          <t>196238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204923</t>
+          <t>206116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>278993</t>
+          <t>279033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>361056</t>
+          <t>355611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>464596</t>
+          <t>462026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3251150</t>
+          <t>3252746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3321573</t>
+          <t>3319014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3370231</t>
+          <t>3370191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3444301</t>
+          <t>3443108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6633612</t>
+          <t>6636182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6737152</t>
+          <t>6742597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>40996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72374</t>
+          <t>72241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115345</t>
+          <t>114057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126337</t>
+          <t>125053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174716</t>
+          <t>175295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>959349</t>
+          <t>959482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>988862</t>
+          <t>990727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1199768</t>
+          <t>1201056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1237311</t>
+          <t>1239615</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2172119</t>
+          <t>2171540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2220498</t>
+          <t>2221782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>54368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38652</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67648</t>
+          <t>67385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72995</t>
+          <t>72524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110867</t>
+          <t>112079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1639459</t>
+          <t>1639045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1665784</t>
+          <t>1665737</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1520025</t>
+          <t>1520288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1549021</t>
+          <t>1549007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3170219</t>
+          <t>3169007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3208091</t>
+          <t>3208562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28321</t>
+          <t>28091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20102</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532113</t>
+          <t>531424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546558</t>
+          <t>545964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>448091</t>
+          <t>448321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>465220</t>
+          <t>465162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>986523</t>
+          <t>987265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1007718</t>
+          <t>1007983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86111</t>
+          <t>84933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127563</t>
+          <t>127475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140887</t>
+          <t>140324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192328</t>
+          <t>190043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>237495</t>
+          <t>235509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301003</t>
+          <t>302413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3148980</t>
+          <t>3149068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3190432</t>
+          <t>3191610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3186869</t>
+          <t>3189154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3238310</t>
+          <t>3238873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6354738</t>
+          <t>6353328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6418246</t>
+          <t>6420232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55751</t>
+          <t>54500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90527</t>
+          <t>88999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176058</t>
+          <t>177674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228953</t>
+          <t>228109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>241447</t>
+          <t>238509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>304594</t>
+          <t>302483</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>883151</t>
+          <t>884679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>917927</t>
+          <t>919178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1107746</t>
+          <t>1108590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1160641</t>
+          <t>1159025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2005782</t>
+          <t>2007893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2068929</t>
+          <t>2071867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59194</t>
+          <t>58429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94701</t>
+          <t>92248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>89127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132975</t>
+          <t>132383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161703</t>
+          <t>162045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>217308</t>
+          <t>217833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1867279</t>
+          <t>1869732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1902786</t>
+          <t>1903551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1622873</t>
+          <t>1623465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1665622</t>
+          <t>1666721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3500520</t>
+          <t>3499995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3556125</t>
+          <t>3555783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23564</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26376</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43157</t>
+          <t>41984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457617</t>
+          <t>457661</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474113</t>
+          <t>474018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>432255</t>
+          <t>432436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>450008</t>
+          <t>449777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>896656</t>
+          <t>897829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>920401</t>
+          <t>921363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134848</t>
+          <t>134931</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187010</t>
+          <t>186700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>292961</t>
+          <t>294250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>363203</t>
+          <t>364973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>446865</t>
+          <t>440794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534063</t>
+          <t>530374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3229829</t>
+          <t>3230139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3281991</t>
+          <t>3281908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3187975</t>
+          <t>3186205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3258217</t>
+          <t>3256928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6433954</t>
+          <t>6437643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6521152</t>
+          <t>6527223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59597</t>
+          <t>58169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86696</t>
+          <t>85729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127271</t>
+          <t>125820</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127173</t>
+          <t>129231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175286</t>
+          <t>174591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>694750</t>
+          <t>696178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>720851</t>
+          <t>720719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>865273</t>
+          <t>866724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>905848</t>
+          <t>906815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1571605</t>
+          <t>1572300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1619718</t>
+          <t>1617660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42971</t>
+          <t>43227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76213</t>
+          <t>77693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54041</t>
+          <t>54040</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88501</t>
+          <t>87447</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107506</t>
+          <t>106155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153648</t>
+          <t>153763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1999199</t>
+          <t>1997719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2032441</t>
+          <t>2032185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1898744</t>
+          <t>1899798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1933204</t>
+          <t>1933205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3909010</t>
+          <t>3908895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3955152</t>
+          <t>3956503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>45139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524054</t>
+          <t>524382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>540049</t>
+          <t>540992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>517038</t>
+          <t>517086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536395</t>
+          <t>535832</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1046062</t>
+          <t>1049020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1071692</t>
+          <t>1071627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98048</t>
+          <t>96875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140993</t>
+          <t>138532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169542</t>
+          <t>167187</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>223629</t>
+          <t>224215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280127</t>
+          <t>278146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349906</t>
+          <t>351146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3235652</t>
+          <t>3238113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3278597</t>
+          <t>3279770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3303433</t>
+          <t>3302847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3357520</t>
+          <t>3359875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6553801</t>
+          <t>6552561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6623580</t>
+          <t>6625561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62816</t>
+          <t>66029</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51258</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76725</t>
+          <t>80920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>133463</t>
+          <t>146060</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119161</t>
+          <t>130652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149221</t>
+          <t>162477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>196280</t>
+          <t>212089</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176126</t>
+          <t>191650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217076</t>
+          <t>235127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>451251</t>
+          <t>511511</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437342</t>
+          <t>496620</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462809</t>
+          <t>524072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>618956</t>
+          <t>672664</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>603198</t>
+          <t>656247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633258</t>
+          <t>688072</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1070206</t>
+          <t>1184175</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1049410</t>
+          <t>1161137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1090360</t>
+          <t>1204614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514067</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514067</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514067</t>
+          <t>577540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752419</t>
+          <t>818724</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752419</t>
+          <t>818724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752419</t>
+          <t>818724</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266486</t>
+          <t>1396264</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266486</t>
+          <t>1396264</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266486</t>
+          <t>1396264</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79677</t>
+          <t>90660</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53861</t>
+          <t>71678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98649</t>
+          <t>113166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96191</t>
+          <t>107998</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71751</t>
+          <t>91395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119766</t>
+          <t>126117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>175868</t>
+          <t>198658</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141726</t>
+          <t>173994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207755</t>
+          <t>226066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2208616</t>
+          <t>2137890</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2189644</t>
+          <t>2115384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2234432</t>
+          <t>2156872</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2140151</t>
+          <t>2061805</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2116576</t>
+          <t>2043686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2164591</t>
+          <t>2078408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4348767</t>
+          <t>4199695</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4316880</t>
+          <t>4172287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4382909</t>
+          <t>4224359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288293</t>
+          <t>2228550</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288293</t>
+          <t>2228550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288293</t>
+          <t>2228550</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236342</t>
+          <t>2169803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236342</t>
+          <t>2169803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236342</t>
+          <t>2169803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524635</t>
+          <t>4398353</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524635</t>
+          <t>4398353</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524635</t>
+          <t>4398353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36649</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>16476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44131</t>
+          <t>49651</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58296</t>
+          <t>63348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>621739</t>
+          <t>684692</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609974</t>
+          <t>673410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630019</t>
+          <t>692885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>641216</t>
+          <t>712120</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633279</t>
+          <t>703152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647421</t>
+          <t>718401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1262955</t>
+          <t>1396813</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248790</t>
+          <t>1383116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1273264</t>
+          <t>1407606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>167378</t>
+          <t>183584</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129970</t>
+          <t>159344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196238</t>
+          <t>214469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>248901</t>
+          <t>276814</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>206116</t>
+          <t>252508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>279033</t>
+          <t>302474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>416279</t>
+          <t>460398</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>355611</t>
+          <t>425069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>462026</t>
+          <t>498291</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3281606</t>
+          <t>3334093</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3252746</t>
+          <t>3303208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3319014</t>
+          <t>3358333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3400323</t>
+          <t>3446590</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3370191</t>
+          <t>3420930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3443108</t>
+          <t>3470896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6681929</t>
+          <t>6780684</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6636182</t>
+          <t>6742791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6742597</t>
+          <t>6816013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448984</t>
+          <t>3517677</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448984</t>
+          <t>3517677</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448984</t>
+          <t>3517677</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3723404</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3723404</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649224</t>
+          <t>3723404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7098208</t>
+          <t>7241082</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7098208</t>
+          <t>7241082</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7098208</t>
+          <t>7241082</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
